--- a/data/swing_user_watchlist_analysis.xlsx
+++ b/data/swing_user_watchlist_analysis.xlsx
@@ -657,7 +657,7 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T16:25:26+08:00</t>
+          <t>2026-08-18T17:58:13+08:00</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T16:25:27+08:00</t>
+          <t>2026-08-18T17:58:13+08:00</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1261,7 @@
       <c r="X2" s="2" t="n"/>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T16:25:26+08:00</t>
+          <t>2026-08-18T17:58:13+08:00</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
       <c r="X3" s="2" t="n"/>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18T16:25:27+08:00</t>
+          <t>2026-08-18T17:58:13+08:00</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">

--- a/data/swing_user_watchlist_analysis.xlsx
+++ b/data/swing_user_watchlist_analysis.xlsx
@@ -15,11 +15,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Definitions" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Overview'!$A$1:$Q$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Performance'!$A$1:$W$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Fundamentals'!$A$1:$Z$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'News'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Archive'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Overview'!$A$1:$Q$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Performance'!$A$1:$W$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Fundamentals'!$A$1:$Z$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'News'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Archive'!$A$1:$I$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -96,9 +96,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -109,6 +106,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -479,12 +479,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:Q1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
@@ -495,10 +495,10 @@
     <col width="17" customWidth="1" min="11" max="11"/>
     <col width="17" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
-    <col width="23" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
     <col width="11" customWidth="1" min="16" max="16"/>
-    <col width="27" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -588,154 +588,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>3008</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>大立光</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-18T16:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>5290</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>5290</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>D0基準</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>83.62</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>80.29000000000001</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>≥20%</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>RangeRotation</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>electronic_components</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-18T17:58:13+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>2383</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>台光電</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-18T16:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>6205</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>6205</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>D0基準</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>76.56</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>74.83</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>≥20%</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>RangeRotation</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>electronic_components</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-18T17:58:13+08:00</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:Q3"/>
+  <autoFilter ref="A1:Q1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -746,7 +600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W3"/>
+  <dimension ref="A1:W1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -775,238 +629,124 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Current</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Return %</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Days</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Stage</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>MFE %</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>MAE %</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Max Close DD %</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>T+5 %</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>T+10 %</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>T+15 %</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>T+20 %</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>T+20 MFE %</t>
         </is>
       </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>T+20 MAE %</t>
         </is>
       </c>
-      <c r="Q1" s="3" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>Target Hit Day</t>
         </is>
       </c>
-      <c r="R1" s="3" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>Stop Hit Day</t>
         </is>
       </c>
-      <c r="S1" s="3" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>Stop First</t>
         </is>
       </c>
-      <c r="T1" s="3" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t>Days to +5%</t>
         </is>
       </c>
-      <c r="U1" s="3" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t>Days to +10%</t>
         </is>
       </c>
-      <c r="V1" s="3" t="inlineStr">
+      <c r="V1" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="W1" s="3" t="inlineStr">
+      <c r="W1" s="2" t="inlineStr">
         <is>
           <t>Error</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>3008</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>大立光</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>5290</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>5290</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>D0基準</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>-4.44</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="2" t="n"/>
-      <c r="L2" s="2" t="n"/>
-      <c r="M2" s="2" t="n"/>
-      <c r="N2" s="2" t="n"/>
-      <c r="O2" s="2" t="n"/>
-      <c r="P2" s="2" t="n"/>
-      <c r="Q2" s="2" t="n"/>
-      <c r="R2" s="2" t="n"/>
-      <c r="S2" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T2" s="2" t="n"/>
-      <c r="U2" s="2" t="n"/>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>Tracking</t>
-        </is>
-      </c>
-      <c r="W2" s="2" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>2383</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>台光電</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>6205</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>6205</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>D0基準</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>4.27</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>-0.5600000000000001</v>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
-      <c r="O3" s="2" t="n"/>
-      <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Tracking</t>
-        </is>
-      </c>
-      <c r="W3" s="2" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:W3"/>
+  <autoFilter ref="A1:W1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1017,16 +757,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z3"/>
+  <dimension ref="A1:Z1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
@@ -1037,331 +777,151 @@
     <col width="18" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="13" customWidth="1" min="17" max="17"/>
-    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
     <col width="14" customWidth="1" min="19" max="19"/>
     <col width="18" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
     <col width="13" customWidth="1" min="22" max="22"/>
     <col width="10" customWidth="1" min="23" max="23"/>
     <col width="10" customWidth="1" min="24" max="24"/>
-    <col width="27" customWidth="1" min="25" max="25"/>
-    <col width="24" customWidth="1" min="26" max="26"/>
+    <col width="10" customWidth="1" min="25" max="25"/>
+    <col width="10" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Market Cap</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Trailing PE</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Forward PE</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>P/B</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>ROE %</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>Gross Margin %</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Operating Margin %</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>Net Margin %</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>Revenue QoQ %</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>Revenue YoY %</t>
         </is>
       </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>Net Income QoQ %</t>
         </is>
       </c>
-      <c r="O1" s="4" t="inlineStr">
+      <c r="O1" s="3" t="inlineStr">
         <is>
           <t>Net Income YoY %</t>
         </is>
       </c>
-      <c r="P1" s="4" t="inlineStr">
+      <c r="P1" s="3" t="inlineStr">
         <is>
           <t>Trailing EPS</t>
         </is>
       </c>
-      <c r="Q1" s="4" t="inlineStr">
+      <c r="Q1" s="3" t="inlineStr">
         <is>
           <t>Forward EPS</t>
         </is>
       </c>
-      <c r="R1" s="4" t="inlineStr">
+      <c r="R1" s="3" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="S1" s="4" t="inlineStr">
+      <c r="S1" s="3" t="inlineStr">
         <is>
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="T1" s="4" t="inlineStr">
+      <c r="T1" s="3" t="inlineStr">
         <is>
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="U1" s="4" t="inlineStr">
+      <c r="U1" s="3" t="inlineStr">
         <is>
           <t>Net Income</t>
         </is>
       </c>
-      <c r="V1" s="4" t="inlineStr">
+      <c r="V1" s="3" t="inlineStr">
         <is>
           <t>Quarter EPS</t>
         </is>
       </c>
-      <c r="W1" s="4" t="inlineStr">
+      <c r="W1" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="X1" s="4" t="inlineStr">
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>Error</t>
         </is>
       </c>
-      <c r="Y1" s="4" t="inlineStr">
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>Updated</t>
         </is>
       </c>
-      <c r="Z1" s="4" t="inlineStr">
+      <c r="Z1" s="3" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>3008</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>大立光</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>691922468864</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>28.123337</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>25.879627</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>3.6123638</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>13.33</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>49.41</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>37.39</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>39.39</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>-9.73</v>
-      </c>
-      <c r="M2" s="2" t="n">
-        <v>-14.64</v>
-      </c>
-      <c r="N2" s="2" t="n">
-        <v>-8.880000000000001</v>
-      </c>
-      <c r="O2" s="2" t="n">
-        <v>-29.43</v>
-      </c>
-      <c r="P2" s="2" t="n">
-        <v>188.1</v>
-      </c>
-      <c r="Q2" s="2" t="n">
-        <v>204.40788</v>
-      </c>
-      <c r="R2" s="2" t="n">
-        <v>15544079000</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>7679569000</v>
-      </c>
-      <c r="T2" s="2" t="n">
-        <v>5812218000</v>
-      </c>
-      <c r="U2" s="2" t="n">
-        <v>6123204000</v>
-      </c>
-      <c r="V2" s="2" t="n">
-        <v>46.11</v>
-      </c>
-      <c r="W2" s="2" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="X2" s="2" t="n"/>
-      <c r="Y2" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-18T17:58:13+08:00</t>
-        </is>
-      </c>
-      <c r="Z2" s="2" t="inlineStr">
-        <is>
-          <t>Yahoo Finance/yfinance</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>2383</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>台光電</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>2223381676032</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>97.71653999999999</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>27.7833</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>38.11378</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>48.38</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>29.42</v>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>21.58</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>16.15</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>32.66</v>
-      </c>
-      <c r="M3" s="2" t="n">
-        <v>78.14</v>
-      </c>
-      <c r="N3" s="2" t="n">
-        <v>42.89</v>
-      </c>
-      <c r="O3" s="2" t="n">
-        <v>101.65</v>
-      </c>
-      <c r="P3" s="2" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="Q3" s="2" t="n">
-        <v>223.3356</v>
-      </c>
-      <c r="R3" s="2" t="n">
-        <v>33067261000</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>9729153000</v>
-      </c>
-      <c r="T3" s="2" t="n">
-        <v>7135369000</v>
-      </c>
-      <c r="U3" s="2" t="n">
-        <v>5339793000</v>
-      </c>
-      <c r="V3" s="2" t="n">
-        <v>14.89</v>
-      </c>
-      <c r="W3" s="2" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="X3" s="2" t="n"/>
-      <c r="Y3" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-18T17:58:13+08:00</t>
-        </is>
-      </c>
-      <c r="Z3" s="2" t="inlineStr">
-        <is>
-          <t>Yahoo Finance/yfinance</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:Z3"/>
+  <autoFilter ref="A1:Z1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1372,169 +932,63 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="48" customWidth="1" min="6" max="6"/>
-    <col width="48" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>Publisher</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>Summary</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>3008</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>大立光</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>no_news</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>2383</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>台光電</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-06T13:41:03Z</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Nvidia Kyber Delay Hits Asian AI Suppliers</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>GuruFocus.com</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Nvidia's next-generation Kyber NVL144 system is reportedly delayed by more than 12 months, triggering sharp regional tech declines.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>https://finance.yahoo.com/technology/ai/articles/nvidia-kyber-delay-hits-asian-134103513.html</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>2383</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>台光電</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2025-12-12T05:31:50Z</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Ignoring AI bubble fears, investors bet Nvidia and Google will fuel Taiwan stocks to record</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Reuters</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Taiwan's tech-heavy stocks show few signs of slowing a rally even as AI bubble worries cast a shadow over global markets, underscoring home-grown confidence in the structural advantages in AI that foreign investors may have overlooked.  Taiwan's benchmark index is poised to breach ​a record 30,000 points in 2026, investors say, extending a three-year surge that has seen the stock market nearly double as the island rides a wave of demand ‌for chips that power artificial intelligence.  While foreign money worries about stretched AI valuations, Taiwanese investors have enthusiastically ploughed into the market.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>https://finance.yahoo.com/news/ignoring-ai-bubble-fears-investors-053150245.html</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H4"/>
+  <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1545,13 +999,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
@@ -1560,54 +1014,165 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Removed</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Last Return %</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Tracked Days</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>Final Stage</t>
         </is>
       </c>
-      <c r="I1" s="6" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>Removal Reason</t>
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18T16:00:00+08:00</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-19T10:04:00+08:00</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="n">
+        <v>5290</v>
+      </c>
+      <c r="F2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>D0基準</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>2383</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-18T16:00:00+08:00</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-19T10:04:00+08:00</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="n">
+        <v>6205</v>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>D0基準</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>3081</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>聯亞</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-19T10:04:00+08:00</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-19T10:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>1480</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>D0基準</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I1"/>
+  <autoFilter ref="A1:I4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1638,120 +1203,120 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>Fixed at the most recent completed trading-day close when the user adds the ticker.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>D0基準</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>No subsequent trading day yet.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>T1-5早期</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>1-5 subsequent trading days.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>T6-10發展</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>6-10 subsequent trading days.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>T11-15中段</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>11-15 subsequent trading days.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>T16-20成熟</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>16-20 subsequent trading days.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>T20後績效驗收</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>More than 20 subsequent trading days.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>MFE/MAE</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Calculated from actual subsequent High/Low relative to the fixed baseline.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>Extension Momentum</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>Observation/ranking only. It does not change v4.0 qualification.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>Removal</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Removed tickers are retained in the archive for audit; history is not deleted.</t>
         </is>

--- a/data/swing_user_watchlist_analysis.xlsx
+++ b/data/swing_user_watchlist_analysis.xlsx
@@ -15,10 +15,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Definitions" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Overview'!$A$1:$Q$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Performance'!$A$1:$W$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Fundamentals'!$A$1:$Z$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'News'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Overview'!$A$1:$Q$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Performance'!$A$1:$W$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Fundamentals'!$A$1:$Z$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'News'!$A$1:$H$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Archive'!$A$1:$I$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -96,6 +96,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -106,9 +109,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -479,12 +479,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
@@ -498,7 +498,7 @@
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="11" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="27" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -588,8 +588,41 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>台半</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T10:06:00+08:00</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n">
+        <v>90.7</v>
+      </c>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
+      <c r="P2" s="2" t="n"/>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T14:22:10+08:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q1"/>
+  <autoFilter ref="A1:Q2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -600,7 +633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W1"/>
+  <dimension ref="A1:W2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -625,128 +658,163 @@
     <col width="13" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="27" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Current</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Return %</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Days</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Stage</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>MFE %</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>MAE %</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Max Close DD %</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>T+5 %</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>T+10 %</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>T+15 %</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>T+20 %</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="O1" s="3" t="inlineStr">
         <is>
           <t>T+20 MFE %</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="P1" s="3" t="inlineStr">
         <is>
           <t>T+20 MAE %</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="Q1" s="3" t="inlineStr">
         <is>
           <t>Target Hit Day</t>
         </is>
       </c>
-      <c r="R1" s="2" t="inlineStr">
+      <c r="R1" s="3" t="inlineStr">
         <is>
           <t>Stop Hit Day</t>
         </is>
       </c>
-      <c r="S1" s="2" t="inlineStr">
+      <c r="S1" s="3" t="inlineStr">
         <is>
           <t>Stop First</t>
         </is>
       </c>
-      <c r="T1" s="2" t="inlineStr">
+      <c r="T1" s="3" t="inlineStr">
         <is>
           <t>Days to +5%</t>
         </is>
       </c>
-      <c r="U1" s="2" t="inlineStr">
+      <c r="U1" s="3" t="inlineStr">
         <is>
           <t>Days to +10%</t>
         </is>
       </c>
-      <c r="V1" s="2" t="inlineStr">
+      <c r="V1" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="W1" s="2" t="inlineStr">
+      <c r="W1" s="3" t="inlineStr">
         <is>
           <t>Error</t>
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>台半</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>90.7</v>
+      </c>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
+      <c r="P2" s="2" t="n"/>
+      <c r="Q2" s="2" t="n"/>
+      <c r="R2" s="2" t="n"/>
+      <c r="S2" s="2" t="n"/>
+      <c r="T2" s="2" t="n"/>
+      <c r="U2" s="2" t="n"/>
+      <c r="V2" s="2" t="n"/>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>tracking_identity_missing</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:W1"/>
+  <autoFilter ref="A1:W2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -757,7 +825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1"/>
+  <dimension ref="A1:Z2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -784,144 +852,188 @@
     <col width="13" customWidth="1" min="22" max="22"/>
     <col width="10" customWidth="1" min="23" max="23"/>
     <col width="10" customWidth="1" min="24" max="24"/>
-    <col width="10" customWidth="1" min="25" max="25"/>
-    <col width="10" customWidth="1" min="26" max="26"/>
+    <col width="27" customWidth="1" min="25" max="25"/>
+    <col width="24" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>Market Cap</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>Trailing PE</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>Forward PE</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>P/B</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>ROE %</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>Gross Margin %</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>Operating Margin %</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>Net Margin %</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>Revenue QoQ %</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>Revenue YoY %</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="N1" s="4" t="inlineStr">
         <is>
           <t>Net Income QoQ %</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="O1" s="4" t="inlineStr">
         <is>
           <t>Net Income YoY %</t>
         </is>
       </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="P1" s="4" t="inlineStr">
         <is>
           <t>Trailing EPS</t>
         </is>
       </c>
-      <c r="Q1" s="3" t="inlineStr">
+      <c r="Q1" s="4" t="inlineStr">
         <is>
           <t>Forward EPS</t>
         </is>
       </c>
-      <c r="R1" s="3" t="inlineStr">
+      <c r="R1" s="4" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="S1" s="3" t="inlineStr">
+      <c r="S1" s="4" t="inlineStr">
         <is>
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="T1" s="3" t="inlineStr">
+      <c r="T1" s="4" t="inlineStr">
         <is>
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="U1" s="3" t="inlineStr">
+      <c r="U1" s="4" t="inlineStr">
         <is>
           <t>Net Income</t>
         </is>
       </c>
-      <c r="V1" s="3" t="inlineStr">
+      <c r="V1" s="4" t="inlineStr">
         <is>
           <t>Quarter EPS</t>
         </is>
       </c>
-      <c r="W1" s="3" t="inlineStr">
+      <c r="W1" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="X1" s="3" t="inlineStr">
+      <c r="X1" s="4" t="inlineStr">
         <is>
           <t>Error</t>
         </is>
       </c>
-      <c r="Y1" s="3" t="inlineStr">
+      <c r="Y1" s="4" t="inlineStr">
         <is>
           <t>Updated</t>
         </is>
       </c>
-      <c r="Z1" s="3" t="inlineStr">
+      <c r="Z1" s="4" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>台半</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
+      <c r="P2" s="2" t="n"/>
+      <c r="Q2" s="2" t="n"/>
+      <c r="R2" s="2" t="n"/>
+      <c r="S2" s="2" t="n"/>
+      <c r="T2" s="2" t="n"/>
+      <c r="U2" s="2" t="n"/>
+      <c r="V2" s="2" t="n"/>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="X2" s="2" t="n"/>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T14:22:10+08:00</t>
+        </is>
+      </c>
+      <c r="Z2" s="2" t="inlineStr">
+        <is>
+          <t>Yahoo Finance/yfinance</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z1"/>
+  <autoFilter ref="A1:Z2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -932,7 +1044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -946,49 +1058,67 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Publisher</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Summary</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>台半</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>no_news</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H1"/>
+  <autoFilter ref="A1:H2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1014,162 +1144,162 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>Removed</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>Last Return %</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>Tracked Days</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>Final Stage</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>Removal Reason</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>3008</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>大立光</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>2026-08-18T16:00:00+08:00</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>2026-08-19T10:04:00+08:00</t>
         </is>
       </c>
-      <c r="E2" s="6" t="n">
+      <c r="E2" s="2" t="n">
         <v>5290</v>
       </c>
-      <c r="F2" s="6" t="n">
+      <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G2" s="6" t="n">
+      <c r="G2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>D0基準</t>
         </is>
       </c>
-      <c r="I2" s="6" t="n"/>
+      <c r="I2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>2383</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>台光電</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>2026-08-18T16:00:00+08:00</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>2026-08-19T10:04:00+08:00</t>
         </is>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="E3" s="2" t="n">
         <v>6205</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="G3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>D0基準</t>
         </is>
       </c>
-      <c r="I3" s="6" t="n"/>
+      <c r="I3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>3081</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>聯亞</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>2026-08-19T10:04:00+08:00</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>2026-08-19T10:16:00+08:00</t>
         </is>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E4" s="2" t="n">
         <v>1480</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="G4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>D0基準</t>
         </is>
       </c>
-      <c r="I4" s="6" t="n"/>
+      <c r="I4" s="2" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I4"/>
@@ -1203,120 +1333,120 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Fixed at the most recent completed trading-day close when the user adds the ticker.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>D0基準</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>No subsequent trading day yet.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>T1-5早期</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>1-5 subsequent trading days.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>T6-10發展</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>6-10 subsequent trading days.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>T11-15中段</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>11-15 subsequent trading days.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>T16-20成熟</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>16-20 subsequent trading days.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>T20後績效驗收</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>More than 20 subsequent trading days.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>MFE/MAE</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Calculated from actual subsequent High/Low relative to the fixed baseline.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Extension Momentum</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Observation/ranking only. It does not change v4.0 qualification.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Removal</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Removed tickers are retained in the archive for audit; history is not deleted.</t>
         </is>

--- a/data/swing_user_watchlist_analysis.xlsx
+++ b/data/swing_user_watchlist_analysis.xlsx
@@ -617,7 +617,7 @@
       <c r="P2" s="2" t="n"/>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20T14:22:10+08:00</t>
+          <t>2026-08-21T14:23:58+08:00</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1023,7 @@
       <c r="X2" s="2" t="n"/>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20T14:22:10+08:00</t>
+          <t>2026-08-21T14:23:58+08:00</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">

--- a/data/swing_user_watchlist_analysis.xlsx
+++ b/data/swing_user_watchlist_analysis.xlsx
@@ -589,7 +589,11 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>5425</t>
+        </is>
+      </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>台半</t>
@@ -600,14 +604,28 @@
           <t>2026-08-20T10:06:00+08:00</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n"/>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
       <c r="E2" s="2" t="n">
-        <v>90.7</v>
-      </c>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="n"/>
+        <v>90.3</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>-4.65</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>T1-5早期</t>
+        </is>
+      </c>
       <c r="J2" s="2" t="n"/>
       <c r="K2" s="2" t="n"/>
       <c r="L2" s="2" t="n"/>
@@ -617,7 +635,7 @@
       <c r="P2" s="2" t="n"/>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21T14:23:58+08:00</t>
+          <t>2026-08-24T14:50:49+08:00</t>
         </is>
       </c>
     </row>
@@ -658,7 +676,7 @@
     <col width="13" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="27" customWidth="1" min="23" max="23"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -779,22 +797,42 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>5425</t>
+        </is>
+      </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>台半</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>90.7</v>
-      </c>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="n"/>
-      <c r="J2" s="2" t="n"/>
+        <v>90.3</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>-4.65</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>T1-5早期</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>-4.65</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>-4.65</v>
+      </c>
       <c r="K2" s="2" t="n"/>
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
@@ -803,15 +841,17 @@
       <c r="P2" s="2" t="n"/>
       <c r="Q2" s="2" t="n"/>
       <c r="R2" s="2" t="n"/>
-      <c r="S2" s="2" t="n"/>
+      <c r="S2" s="2" t="b">
+        <v>0</v>
+      </c>
       <c r="T2" s="2" t="n"/>
       <c r="U2" s="2" t="n"/>
-      <c r="V2" s="2" t="n"/>
-      <c r="W2" s="2" t="inlineStr">
-        <is>
-          <t>tracking_identity_missing</t>
-        </is>
-      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:W2"/>
@@ -830,8 +870,8 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -845,10 +885,10 @@
     <col width="18" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="13" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
     <col width="14" customWidth="1" min="19" max="19"/>
     <col width="18" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
     <col width="13" customWidth="1" min="22" max="22"/>
     <col width="10" customWidth="1" min="23" max="23"/>
     <col width="10" customWidth="1" min="24" max="24"/>
@@ -989,32 +1029,78 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>5425</t>
+        </is>
+      </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>台半</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="n"/>
-      <c r="J2" s="2" t="n"/>
-      <c r="K2" s="2" t="n"/>
-      <c r="L2" s="2" t="n"/>
-      <c r="M2" s="2" t="n"/>
-      <c r="N2" s="2" t="n"/>
-      <c r="O2" s="2" t="n"/>
-      <c r="P2" s="2" t="n"/>
-      <c r="Q2" s="2" t="n"/>
-      <c r="R2" s="2" t="n"/>
-      <c r="S2" s="2" t="n"/>
-      <c r="T2" s="2" t="n"/>
-      <c r="U2" s="2" t="n"/>
-      <c r="V2" s="2" t="n"/>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>21311936512</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>37.59825</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>13.601895</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>2.754671</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>31.29</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>-2.61</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>-17.15</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>46.47</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>4390420000</v>
+      </c>
+      <c r="S2" s="2" t="n">
+        <v>1373706000</v>
+      </c>
+      <c r="T2" s="2" t="n">
+        <v>381503000</v>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>170603000</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>0.69769</v>
+      </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
           <t>ok</t>
@@ -1023,7 +1109,7 @@
       <c r="X2" s="2" t="n"/>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21T14:23:58+08:00</t>
+          <t>2026-08-24T14:50:49+08:00</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -1049,11 +1135,11 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
+    <col width="48" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -1100,20 +1186,44 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>5425</t>
+        </is>
+      </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>台半</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17T14:08:26Z</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>TSM Stock Falls To Two-Month Low Amid Semiconductor Sell-Off Despite Wave Of Price Target Hikes</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Stocktwits</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>TSMC’s stock traded below $400 for the first time since May, marking the seventh straight day of losses for the shares.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>https://stocktwits.com/news-articles/markets/equity/tsm-stock-two-month-low-semiconductor-selloff-price-target-hikes/cZZ7laVR7MG</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>no_news</t>
+          <t>ok</t>
         </is>
       </c>
     </row>

--- a/data/swing_user_watchlist_analysis.xlsx
+++ b/data/swing_user_watchlist_analysis.xlsx
@@ -15,10 +15,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Definitions" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Overview'!$A$1:$Q$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Performance'!$A$1:$W$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Fundamentals'!$A$1:$Z$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'News'!$A$1:$H$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Overview'!$A$1:$Q$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Performance'!$A$1:$W$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Fundamentals'!$A$1:$Z$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'News'!$A$1:$H$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Archive'!$A$1:$I$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -613,13 +613,13 @@
         <v>90.3</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>86.09999999999999</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>-4.65</v>
+        <v>-2.66</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
@@ -635,12 +635,63 @@
       <c r="P2" s="2" t="n"/>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24T14:50:49+08:00</t>
+          <t>2026-08-25T14:23:09+08:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>6488</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>環球晶</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24T00:00:00+08:00</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>1010</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>980</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>-2.97</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>T1-5早期</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
+      <c r="P3" s="2" t="n"/>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25T14:23:09+08:00</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q2"/>
+  <autoFilter ref="A1:Q3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -651,7 +702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:W3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -811,13 +862,13 @@
         <v>90.3</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>86.09999999999999</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-4.65</v>
+        <v>-2.66</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -828,7 +879,7 @@
         <v>5.98</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-4.65</v>
+        <v>-7.2</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>-4.65</v>
@@ -853,8 +904,65 @@
       </c>
       <c r="W2" s="2" t="n"/>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>6488</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>環球晶</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>1010</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>980</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>-2.97</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>T1-5早期</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>-6.93</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>-2.97</v>
+      </c>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
+      <c r="P3" s="2" t="n"/>
+      <c r="Q3" s="2" t="n"/>
+      <c r="R3" s="2" t="n"/>
+      <c r="S3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" s="2" t="n"/>
+      <c r="U3" s="2" t="n"/>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Tracking</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:W2"/>
+  <autoFilter ref="A1:W3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -865,16 +973,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z2"/>
+  <dimension ref="A1:Z3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
@@ -885,10 +993,10 @@
     <col width="18" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="13" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="18" max="18"/>
     <col width="14" customWidth="1" min="19" max="19"/>
     <col width="18" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
     <col width="13" customWidth="1" min="22" max="22"/>
     <col width="10" customWidth="1" min="23" max="23"/>
     <col width="10" customWidth="1" min="24" max="24"/>
@@ -1045,16 +1153,16 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>21311936512</v>
+        <v>21757483008</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>37.59825</v>
+        <v>30</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>13.601895</v>
+        <v>13.886256</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>2.754671</v>
+        <v>2.8122602</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>13.2</v>
@@ -1081,7 +1189,7 @@
         <v>46.47</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>2.29</v>
+        <v>2.93</v>
       </c>
       <c r="Q2" s="2" t="n">
         <v>6.33</v>
@@ -1109,7 +1217,7 @@
       <c r="X2" s="2" t="n"/>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24T14:50:49+08:00</t>
+          <t>2026-08-25T14:23:09+08:00</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -1118,8 +1226,98 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>6488</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>環球晶</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>468551467008</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>47.572815</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>29.751125</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>4.844195</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>20.83</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>13.56</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>-3.57</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>-14.43</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>-14.01</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>296</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>32.93993</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>13984798000</v>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>2913500000</v>
+      </c>
+      <c r="T3" s="2" t="n">
+        <v>1475474000</v>
+      </c>
+      <c r="U3" s="2" t="n">
+        <v>1895821000</v>
+      </c>
+      <c r="V3" s="2" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="X3" s="2" t="n"/>
+      <c r="Y3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25T14:23:09+08:00</t>
+        </is>
+      </c>
+      <c r="Z3" s="2" t="inlineStr">
+        <is>
+          <t>Yahoo Finance/yfinance</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z2"/>
+  <autoFilter ref="A1:Z3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1130,14 +1328,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="48" customWidth="1" min="6" max="6"/>
     <col width="48" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -1227,8 +1425,134 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>6488</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>環球晶</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09T18:29:34Z</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Direxion Daily Semiconductor Bull 3X ETF Explodes</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Motley Fool</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>If you like semiconductor stocks, you're going to love what's happening at Direxion today.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fool.com/investing/2026/07/09/direxion-daily-semiconductor-bull-3x-etf-explodes/</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>6488</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>環球晶</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09T18:11:00Z</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Micron Unveils $250 Billion Spending Plan. BofA Says Buy.</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Barrons.com</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Micron stock has dropped from levels of more than $1,200 and BofA analysts say there's a chance to buy at a discount.</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.barrons.com/articles/micron-stock-price-analyst-buy-spending-19ebab1a?siteid=yhoof2&amp;yptr=yahoo</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>6488</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>環球晶</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09T13:57:18Z</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>GlobalFoundries Shares Rise After Micron Expands U.S. Semiconductor Supply Chain Investment (GFS)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>InvestorsHub</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Micron Investment Boosts Confidence in U. S.</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>https://investorshub.advfn.com/market-news/article/31596/globalfoundries-shares-rise-after-micron-expands-u-s-semiconductor-supply-chain-investment-gfs</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H2"/>
+  <autoFilter ref="A1:H5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/swing_user_watchlist_analysis.xlsx
+++ b/data/swing_user_watchlist_analysis.xlsx
@@ -613,13 +613,13 @@
         <v>90.3</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>87.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>-2.66</v>
+        <v>6.98</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
       <c r="P2" s="2" t="n"/>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25T14:23:09+08:00</t>
+          <t>2026-08-26T14:24:04+08:00</t>
         </is>
       </c>
     </row>
@@ -664,13 +664,13 @@
         <v>1010</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>980</v>
+        <v>949</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>-2.97</v>
+        <v>-6.04</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
       <c r="P3" s="2" t="n"/>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25T14:23:09+08:00</t>
+          <t>2026-08-26T14:24:05+08:00</t>
         </is>
       </c>
     </row>
@@ -862,13 +862,13 @@
         <v>90.3</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>87.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-2.66</v>
+        <v>6.98</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>5.98</v>
+        <v>6.98</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>-7.2</v>
@@ -895,7 +895,9 @@
       <c r="S2" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="T2" s="2" t="n"/>
+      <c r="T2" s="2" t="n">
+        <v>4</v>
+      </c>
       <c r="U2" s="2" t="n"/>
       <c r="V2" s="2" t="inlineStr">
         <is>
@@ -919,13 +921,13 @@
         <v>1010</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>980</v>
+        <v>949</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-2.97</v>
+        <v>-6.04</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -939,7 +941,7 @@
         <v>-6.93</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>-2.97</v>
+        <v>-6.04</v>
       </c>
       <c r="K3" s="2" t="n"/>
       <c r="L3" s="2" t="n"/>
@@ -982,7 +984,7 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
@@ -1153,16 +1155,16 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>21757483008</v>
+        <v>23910955008</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>30</v>
+        <v>32.96928</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>13.886256</v>
+        <v>15.260663</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>2.8122602</v>
+        <v>3.076923</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>13.2</v>
@@ -1217,7 +1219,7 @@
       <c r="X2" s="2" t="n"/>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25T14:23:09+08:00</t>
+          <t>2026-08-26T14:24:04+08:00</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -1243,16 +1245,16 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>468551467008</v>
+        <v>453729943552</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>47.572815</v>
+        <v>46.112732</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>29.751125</v>
+        <v>28.810019</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>4.844195</v>
+        <v>4.69096</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>10.85</v>
@@ -1279,7 +1281,7 @@
         <v>296</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>20.6</v>
+        <v>20.58</v>
       </c>
       <c r="Q3" s="2" t="n">
         <v>32.93993</v>
@@ -1307,7 +1309,7 @@
       <c r="X3" s="2" t="n"/>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25T14:23:09+08:00</t>
+          <t>2026-08-26T14:24:05+08:00</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">

--- a/data/swing_user_watchlist_analysis.xlsx
+++ b/data/swing_user_watchlist_analysis.xlsx
@@ -613,13 +613,13 @@
         <v>90.3</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>96.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>6.98</v>
+        <v>5.43</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
       <c r="P2" s="2" t="n"/>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26T14:24:04+08:00</t>
+          <t>2026-08-27T14:24:28+08:00</t>
         </is>
       </c>
     </row>
@@ -664,13 +664,13 @@
         <v>1010</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>949</v>
+        <v>958</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>-6.04</v>
+        <v>-5.15</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
       <c r="P3" s="2" t="n"/>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26T14:24:05+08:00</t>
+          <t>2026-08-27T14:24:29+08:00</t>
         </is>
       </c>
     </row>
@@ -862,13 +862,13 @@
         <v>90.3</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>96.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>6.98</v>
+        <v>5.43</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>6.98</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>-7.2</v>
@@ -884,7 +884,9 @@
       <c r="J2" s="2" t="n">
         <v>-4.65</v>
       </c>
-      <c r="K2" s="2" t="n"/>
+      <c r="K2" s="2" t="n">
+        <v>5.43</v>
+      </c>
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
       <c r="N2" s="2" t="n"/>
@@ -921,13 +923,13 @@
         <v>1010</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>949</v>
+        <v>958</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-6.04</v>
+        <v>-5.15</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -938,7 +940,7 @@
         <v>2.48</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>-6.93</v>
+        <v>-8.42</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>-6.04</v>
@@ -984,7 +986,7 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
@@ -1155,16 +1157,16 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>23910955008</v>
+        <v>23564419072</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>32.96928</v>
+        <v>32.491467</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>15.260663</v>
+        <v>15.0394945</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>3.076923</v>
+        <v>3.0323298</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>13.2</v>
@@ -1219,7 +1221,7 @@
       <c r="X2" s="2" t="n"/>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26T14:24:04+08:00</t>
+          <t>2026-08-27T14:24:28+08:00</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -1245,16 +1247,16 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>453729943552</v>
+        <v>458032939008</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>46.112732</v>
+        <v>46.52744</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>28.810019</v>
+        <v>29.083244</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>4.69096</v>
+        <v>4.7354474</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>10.85</v>
@@ -1281,7 +1283,7 @@
         <v>296</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>20.58</v>
+        <v>20.59</v>
       </c>
       <c r="Q3" s="2" t="n">
         <v>32.93993</v>
@@ -1309,7 +1311,7 @@
       <c r="X3" s="2" t="n"/>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26T14:24:05+08:00</t>
+          <t>2026-08-27T14:24:29+08:00</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">

--- a/data/swing_user_watchlist_analysis.xlsx
+++ b/data/swing_user_watchlist_analysis.xlsx
@@ -613,17 +613,17 @@
         <v>90.3</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>95.2</v>
+        <v>96.3</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>5.43</v>
+        <v>6.64</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>T1-5早期</t>
+          <t>T6-10發展</t>
         </is>
       </c>
       <c r="J2" s="2" t="n"/>
@@ -635,7 +635,7 @@
       <c r="P2" s="2" t="n"/>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27T14:24:28+08:00</t>
+          <t>2026-08-28T14:23:44+08:00</t>
         </is>
       </c>
     </row>
@@ -664,13 +664,13 @@
         <v>1010</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>958</v>
+        <v>972</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>-5.15</v>
+        <v>-3.76</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
       <c r="P3" s="2" t="n"/>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27T14:24:29+08:00</t>
+          <t>2026-08-28T14:23:45+08:00</t>
         </is>
       </c>
     </row>
@@ -862,21 +862,21 @@
         <v>90.3</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>95.2</v>
+        <v>96.3</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>5.43</v>
+        <v>6.64</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>T1-5早期</t>
+          <t>T6-10發展</t>
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>8.859999999999999</v>
+        <v>15.73</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>-7.2</v>
@@ -900,7 +900,9 @@
       <c r="T2" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="U2" s="2" t="n"/>
+      <c r="U2" s="2" t="n">
+        <v>6</v>
+      </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
           <t>Tracking</t>
@@ -923,13 +925,13 @@
         <v>1010</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>958</v>
+        <v>972</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-5.15</v>
+        <v>-3.76</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -1157,16 +1159,16 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>23564419072</v>
+        <v>23836696576</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>32.491467</v>
+        <v>32.866894</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>15.0394945</v>
+        <v>15.213271</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>3.0323298</v>
+        <v>3.0673676</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>13.2</v>
@@ -1221,7 +1223,7 @@
       <c r="X2" s="2" t="n"/>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27T14:24:28+08:00</t>
+          <t>2026-08-28T14:23:44+08:00</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -1247,16 +1249,16 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>458032939008</v>
+        <v>464726556672</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>46.52744</v>
+        <v>47.184464</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>29.083244</v>
+        <v>29.508259</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>4.7354474</v>
+        <v>4.8046503</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>10.85</v>
@@ -1283,7 +1285,7 @@
         <v>296</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>20.59</v>
+        <v>20.6</v>
       </c>
       <c r="Q3" s="2" t="n">
         <v>32.93993</v>
@@ -1311,7 +1313,7 @@
       <c r="X3" s="2" t="n"/>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27T14:24:29+08:00</t>
+          <t>2026-08-28T14:23:45+08:00</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">

--- a/data/swing_user_watchlist_analysis.xlsx
+++ b/data/swing_user_watchlist_analysis.xlsx
@@ -613,13 +613,13 @@
         <v>90.3</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>96.3</v>
+        <v>94.8</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>6.64</v>
+        <v>4.98</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
       <c r="P2" s="2" t="n"/>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28T14:23:44+08:00</t>
+          <t>2026-08-31T14:25:21+08:00</t>
         </is>
       </c>
     </row>
@@ -664,13 +664,13 @@
         <v>1010</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>972</v>
+        <v>912</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>-3.76</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
       <c r="P3" s="2" t="n"/>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28T14:23:45+08:00</t>
+          <t>2026-08-31T14:25:22+08:00</t>
         </is>
       </c>
     </row>
@@ -862,13 +862,13 @@
         <v>90.3</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>96.3</v>
+        <v>94.8</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>6.64</v>
+        <v>4.98</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -925,13 +925,13 @@
         <v>1010</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>972</v>
+        <v>912</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-3.76</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -942,12 +942,14 @@
         <v>2.48</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>-8.42</v>
+        <v>-13.37</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>-6.04</v>
-      </c>
-      <c r="K3" s="2" t="n"/>
+        <v>-9.699999999999999</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>-9.699999999999999</v>
+      </c>
       <c r="L3" s="2" t="n"/>
       <c r="M3" s="2" t="n"/>
       <c r="N3" s="2" t="n"/>
@@ -1159,16 +1161,16 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>23836696576</v>
+        <v>23465408512</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>32.866894</v>
+        <v>32.35495</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>15.213271</v>
+        <v>14.976304</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>3.0673676</v>
+        <v>3.0195892</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>13.2</v>
@@ -1223,7 +1225,7 @@
       <c r="X2" s="2" t="n"/>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28T14:23:44+08:00</t>
+          <t>2026-08-31T14:25:21+08:00</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -1249,16 +1251,16 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>464726556672</v>
+        <v>436039712768</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>47.184464</v>
+        <v>44.250362</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>29.508259</v>
+        <v>27.686762</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>4.8046503</v>
+        <v>4.508067</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>10.85</v>
@@ -1285,7 +1287,7 @@
         <v>296</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>20.6</v>
+        <v>20.61</v>
       </c>
       <c r="Q3" s="2" t="n">
         <v>32.93993</v>
@@ -1313,7 +1315,7 @@
       <c r="X3" s="2" t="n"/>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28T14:23:45+08:00</t>
+          <t>2026-08-31T14:25:22+08:00</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">

--- a/data/swing_user_watchlist_analysis.xlsx
+++ b/data/swing_user_watchlist_analysis.xlsx
@@ -613,13 +613,13 @@
         <v>90.3</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>94.8</v>
+        <v>95.2</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>4.98</v>
+        <v>5.43</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
       <c r="P2" s="2" t="n"/>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31T14:25:21+08:00</t>
+          <t>2026-09-01T14:23:30+08:00</t>
         </is>
       </c>
     </row>
@@ -664,17 +664,17 @@
         <v>1010</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>912</v>
+        <v>994</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>-9.699999999999999</v>
+        <v>-1.58</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>T1-5早期</t>
+          <t>T6-10發展</t>
         </is>
       </c>
       <c r="J3" s="2" t="n"/>
@@ -686,7 +686,7 @@
       <c r="P3" s="2" t="n"/>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31T14:25:22+08:00</t>
+          <t>2026-09-01T14:23:31+08:00</t>
         </is>
       </c>
     </row>
@@ -862,13 +862,13 @@
         <v>90.3</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>94.8</v>
+        <v>95.2</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4.98</v>
+        <v>5.43</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -925,17 +925,17 @@
         <v>1010</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>912</v>
+        <v>994</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-9.699999999999999</v>
+        <v>-1.58</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>T1-5早期</t>
+          <t>T6-10發展</t>
         </is>
       </c>
       <c r="H3" s="2" t="n">
@@ -1161,16 +1161,16 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>23465408512</v>
+        <v>23564419072</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>32.35495</v>
+        <v>32.491467</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>14.976304</v>
+        <v>15.0394945</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>3.0195892</v>
+        <v>3.0323298</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>13.2</v>
@@ -1225,7 +1225,7 @@
       <c r="X2" s="2" t="n"/>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31T14:25:21+08:00</t>
+          <t>2026-09-01T14:23:30+08:00</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -1251,16 +1251,16 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>436039712768</v>
+        <v>475245051904</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>44.250362</v>
+        <v>48.440544</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>27.686762</v>
+        <v>30.176142</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>4.508067</v>
+        <v>4.913398</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>10.85</v>
@@ -1287,7 +1287,7 @@
         <v>296</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>20.61</v>
+        <v>20.52</v>
       </c>
       <c r="Q3" s="2" t="n">
         <v>32.93993</v>
@@ -1315,7 +1315,7 @@
       <c r="X3" s="2" t="n"/>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31T14:25:22+08:00</t>
+          <t>2026-09-01T14:23:31+08:00</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">

--- a/data/swing_user_watchlist_analysis.xlsx
+++ b/data/swing_user_watchlist_analysis.xlsx
@@ -613,13 +613,13 @@
         <v>90.3</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>95.2</v>
+        <v>92.5</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>5.43</v>
+        <v>2.44</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
       <c r="P2" s="2" t="n"/>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01T14:23:30+08:00</t>
+          <t>2026-09-02T14:24:02+08:00</t>
         </is>
       </c>
     </row>
@@ -664,13 +664,13 @@
         <v>1010</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>994</v>
+        <v>967</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>-1.58</v>
+        <v>-4.26</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
       <c r="P3" s="2" t="n"/>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01T14:23:31+08:00</t>
+          <t>2026-09-02T14:24:03+08:00</t>
         </is>
       </c>
     </row>
@@ -862,13 +862,13 @@
         <v>90.3</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>95.2</v>
+        <v>92.5</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>5.43</v>
+        <v>2.44</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -925,13 +925,13 @@
         <v>1010</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>994</v>
+        <v>967</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-1.58</v>
+        <v>-4.26</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -1161,16 +1161,16 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>23564419072</v>
+        <v>22896099328</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>32.491467</v>
+        <v>31.569965</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>15.0394945</v>
+        <v>14.612954</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>3.0323298</v>
+        <v>2.9463289</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>13.2</v>
@@ -1225,7 +1225,7 @@
       <c r="X2" s="2" t="n"/>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01T14:23:30+08:00</t>
+          <t>2026-09-02T14:24:02+08:00</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -1251,16 +1251,16 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>475245051904</v>
+        <v>462335967232</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>48.440544</v>
+        <v>46.987366</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>30.176142</v>
+        <v>29.356468</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>4.913398</v>
+        <v>4.7799354</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>10.85</v>
@@ -1287,7 +1287,7 @@
         <v>296</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>20.52</v>
+        <v>20.58</v>
       </c>
       <c r="Q3" s="2" t="n">
         <v>32.93993</v>
@@ -1315,7 +1315,7 @@
       <c r="X3" s="2" t="n"/>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-01T14:23:31+08:00</t>
+          <t>2026-09-02T14:24:03+08:00</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">

--- a/data/swing_user_watchlist_analysis.xlsx
+++ b/data/swing_user_watchlist_analysis.xlsx
@@ -613,13 +613,13 @@
         <v>90.3</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>92.5</v>
+        <v>91.2</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>2.44</v>
+        <v>1</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
       <c r="P2" s="2" t="n"/>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02T14:24:02+08:00</t>
+          <t>2026-09-03T14:23:41+08:00</t>
         </is>
       </c>
     </row>
@@ -664,13 +664,13 @@
         <v>1010</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>967</v>
+        <v>927</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>-4.26</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
       <c r="P3" s="2" t="n"/>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02T14:24:03+08:00</t>
+          <t>2026-09-03T14:23:42+08:00</t>
         </is>
       </c>
     </row>
@@ -862,13 +862,13 @@
         <v>90.3</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>92.5</v>
+        <v>91.2</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2.44</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -882,12 +882,14 @@
         <v>-7.2</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-4.65</v>
+        <v>-5.59</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>5.43</v>
       </c>
-      <c r="L2" s="2" t="n"/>
+      <c r="L2" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="M2" s="2" t="n"/>
       <c r="N2" s="2" t="n"/>
       <c r="O2" s="2" t="n"/>
@@ -925,13 +927,13 @@
         <v>1010</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>967</v>
+        <v>927</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-4.26</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -990,7 +992,7 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
@@ -1161,16 +1163,16 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>22896099328</v>
+        <v>22574315520</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>31.569965</v>
+        <v>31.126278</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>14.612954</v>
+        <v>14.407582</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>2.9463289</v>
+        <v>2.904921</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>13.2</v>
@@ -1225,7 +1227,7 @@
       <c r="X2" s="2" t="n"/>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02T14:24:02+08:00</t>
+          <t>2026-09-03T14:23:41+08:00</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -1251,16 +1253,16 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>462335967232</v>
+        <v>443211415552</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>46.987366</v>
+        <v>45</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>29.356468</v>
+        <v>28.142136</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>4.7799354</v>
+        <v>4.582213</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>10.85</v>
@@ -1287,7 +1289,7 @@
         <v>296</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>20.58</v>
+        <v>20.6</v>
       </c>
       <c r="Q3" s="2" t="n">
         <v>32.93993</v>
@@ -1315,7 +1317,7 @@
       <c r="X3" s="2" t="n"/>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02T14:24:03+08:00</t>
+          <t>2026-09-03T14:23:42+08:00</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">

--- a/data/swing_user_watchlist_analysis.xlsx
+++ b/data/swing_user_watchlist_analysis.xlsx
@@ -613,17 +613,17 @@
         <v>90.3</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>91.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1</v>
+        <v>2.88</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>T6-10發展</t>
+          <t>T11-15中段</t>
         </is>
       </c>
       <c r="J2" s="2" t="n"/>
@@ -635,7 +635,7 @@
       <c r="P2" s="2" t="n"/>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03T14:23:41+08:00</t>
+          <t>2026-09-04T14:24:25+08:00</t>
         </is>
       </c>
     </row>
@@ -664,13 +664,13 @@
         <v>1010</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>927</v>
+        <v>981</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>-8.220000000000001</v>
+        <v>-2.87</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
       <c r="P3" s="2" t="n"/>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03T14:23:42+08:00</t>
+          <t>2026-09-04T14:24:26+08:00</t>
         </is>
       </c>
     </row>
@@ -862,17 +862,17 @@
         <v>90.3</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>91.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1</v>
+        <v>2.88</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>T6-10發展</t>
+          <t>T11-15中段</t>
         </is>
       </c>
       <c r="H2" s="2" t="n">
@@ -927,13 +927,13 @@
         <v>1010</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>927</v>
+        <v>981</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-8.220000000000001</v>
+        <v>-2.87</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -1163,16 +1163,16 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>22574315520</v>
+        <v>22995109888</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>31.126278</v>
+        <v>31.706484</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>14.407582</v>
+        <v>14.676146</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>2.904921</v>
+        <v>2.95907</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>13.2</v>
@@ -1227,7 +1227,7 @@
       <c r="X2" s="2" t="n"/>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03T14:23:41+08:00</t>
+          <t>2026-09-04T14:24:25+08:00</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -1253,16 +1253,16 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>443211415552</v>
+        <v>469029552128</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>45</v>
+        <v>47.667637</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>28.142136</v>
+        <v>29.781485</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>4.582213</v>
+        <v>4.849138</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>10.85</v>
@@ -1289,7 +1289,7 @@
         <v>296</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>20.6</v>
+        <v>20.58</v>
       </c>
       <c r="Q3" s="2" t="n">
         <v>32.93993</v>
@@ -1317,7 +1317,7 @@
       <c r="X3" s="2" t="n"/>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03T14:23:42+08:00</t>
+          <t>2026-09-04T14:24:26+08:00</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">

--- a/data/swing_user_watchlist_analysis.xlsx
+++ b/data/swing_user_watchlist_analysis.xlsx
@@ -613,13 +613,13 @@
         <v>90.3</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>92.90000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>2.88</v>
+        <v>2.33</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
       <c r="P2" s="2" t="n"/>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04T14:24:25+08:00</t>
+          <t>2026-09-07T14:24:51+08:00</t>
         </is>
       </c>
     </row>
@@ -664,13 +664,13 @@
         <v>1010</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>981</v>
+        <v>971</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>-2.87</v>
+        <v>-3.86</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
       <c r="P3" s="2" t="n"/>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04T14:24:26+08:00</t>
+          <t>2026-09-07T14:24:51+08:00</t>
         </is>
       </c>
     </row>
@@ -862,13 +862,13 @@
         <v>90.3</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>92.90000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2.88</v>
+        <v>2.33</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -927,13 +927,13 @@
         <v>1010</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>981</v>
+        <v>971</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-2.87</v>
+        <v>-3.86</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -952,7 +952,9 @@
       <c r="K3" s="2" t="n">
         <v>-9.699999999999999</v>
       </c>
-      <c r="L3" s="2" t="n"/>
+      <c r="L3" s="2" t="n">
+        <v>-3.86</v>
+      </c>
       <c r="M3" s="2" t="n"/>
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
@@ -992,7 +994,7 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
@@ -1159,44 +1161,44 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>22995109888</v>
+        <v>22871347200</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>31.706484</v>
+        <v>31.535835</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>14.676146</v>
+        <v>14.597157</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>2.95907</v>
+        <v>2.9603052</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>13.2</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>31.29</v>
+        <v>29.62</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>8.69</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>3.89</v>
+        <v>3.98</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0.06</v>
+        <v>15.71</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>-2.61</v>
+        <v>7.89</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>-17.15</v>
+        <v>18.37</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>46.47</v>
+        <v>390.37</v>
       </c>
       <c r="P2" s="2" t="n">
         <v>2.93</v>
@@ -1205,19 +1207,19 @@
         <v>6.33</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>4390420000</v>
+        <v>5080089000</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>1373706000</v>
+        <v>1504950000</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>381503000</v>
+        <v>475622000</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>170603000</v>
+        <v>201935000</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>0.69769</v>
+        <v>0.82</v>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
@@ -1227,7 +1229,7 @@
       <c r="X2" s="2" t="n"/>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04T14:24:25+08:00</t>
+          <t>2026-09-07T14:24:51+08:00</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -1249,65 +1251,65 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>469029552128</v>
+        <v>464248438784</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>47.667637</v>
+        <v>47.13592</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>29.781485</v>
+        <v>29.477901</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>4.849138</v>
+        <v>4.7997074</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>10.85</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>20.83</v>
+        <v>20.64</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>10.55</v>
+        <v>9.35</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>13.56</v>
+        <v>24.84</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-3.57</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>-14.43</v>
+        <v>-2.44</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>-14.01</v>
+        <v>99.34</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>296</v>
+        <v>159.5</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>20.58</v>
+        <v>20.6</v>
       </c>
       <c r="Q3" s="2" t="n">
         <v>32.93993</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>13984798000</v>
+        <v>15214310000</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>2913500000</v>
+        <v>3140439000</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>1475474000</v>
+        <v>1422221000</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>1895821000</v>
+        <v>3779084000</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>3.96</v>
+        <v>7.9</v>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
@@ -1317,7 +1319,7 @@
       <c r="X3" s="2" t="n"/>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04T14:24:26+08:00</t>
+          <t>2026-09-07T14:24:51+08:00</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">

--- a/data/swing_user_watchlist_analysis.xlsx
+++ b/data/swing_user_watchlist_analysis.xlsx
@@ -613,13 +613,13 @@
         <v>90.3</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>92.40000000000001</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>2.33</v>
+        <v>-0.78</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
       <c r="P2" s="2" t="n"/>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T14:24:51+08:00</t>
+          <t>2026-09-08T14:23:12+08:00</t>
         </is>
       </c>
     </row>
@@ -664,17 +664,17 @@
         <v>1010</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>971</v>
+        <v>955</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>-3.86</v>
+        <v>-5.45</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>T6-10發展</t>
+          <t>T11-15中段</t>
         </is>
       </c>
       <c r="J3" s="2" t="n"/>
@@ -686,7 +686,7 @@
       <c r="P3" s="2" t="n"/>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T14:24:51+08:00</t>
+          <t>2026-09-08T14:23:13+08:00</t>
         </is>
       </c>
     </row>
@@ -862,13 +862,13 @@
         <v>90.3</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>92.40000000000001</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2.33</v>
+        <v>-0.78</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>-7.2</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-5.59</v>
+        <v>-7.25</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>5.43</v>
@@ -927,17 +927,17 @@
         <v>1010</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>971</v>
+        <v>955</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-3.86</v>
+        <v>-5.45</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>T6-10發展</t>
+          <t>T11-15中段</t>
         </is>
       </c>
       <c r="H3" s="2" t="n">
@@ -1165,16 +1165,16 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>22871347200</v>
+        <v>22178275328</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>31.535835</v>
+        <v>30.580204</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>14.597157</v>
+        <v>14.154819</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>2.9603052</v>
+        <v>2.8705988</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>13.2</v>
@@ -1229,7 +1229,7 @@
       <c r="X2" s="2" t="n"/>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T14:24:51+08:00</t>
+          <t>2026-09-08T14:23:12+08:00</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -1255,16 +1255,16 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>464248438784</v>
+        <v>456598618112</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>47.13592</v>
+        <v>46.381737</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>29.477901</v>
+        <v>28.992168</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>4.7997074</v>
+        <v>4.7206182</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>10.85</v>
@@ -1291,7 +1291,7 @@
         <v>159.5</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>20.6</v>
+        <v>20.59</v>
       </c>
       <c r="Q3" s="2" t="n">
         <v>32.93993</v>
@@ -1319,7 +1319,7 @@
       <c r="X3" s="2" t="n"/>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07T14:24:51+08:00</t>
+          <t>2026-09-08T14:23:13+08:00</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">

--- a/data/swing_user_watchlist_analysis.xlsx
+++ b/data/swing_user_watchlist_analysis.xlsx
@@ -613,13 +613,13 @@
         <v>90.3</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>89.59999999999999</v>
+        <v>89.3</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>-0.78</v>
+        <v>-1.11</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
       <c r="P2" s="2" t="n"/>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T14:23:12+08:00</t>
+          <t>2026-09-10T14:25:37+08:00</t>
         </is>
       </c>
     </row>
@@ -664,13 +664,13 @@
         <v>1010</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>955</v>
+        <v>917</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>-5.45</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
       <c r="P3" s="2" t="n"/>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T14:23:13+08:00</t>
+          <t>2026-09-10T14:25:38+08:00</t>
         </is>
       </c>
     </row>
@@ -862,13 +862,13 @@
         <v>90.3</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>89.59999999999999</v>
+        <v>89.3</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-0.78</v>
+        <v>-1.11</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>-7.2</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-7.25</v>
+        <v>-7.56</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>5.43</v>
@@ -890,7 +890,9 @@
       <c r="L2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M2" s="2" t="n"/>
+      <c r="M2" s="2" t="n">
+        <v>-1.11</v>
+      </c>
       <c r="N2" s="2" t="n"/>
       <c r="O2" s="2" t="n"/>
       <c r="P2" s="2" t="n"/>
@@ -927,13 +929,13 @@
         <v>1010</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>955</v>
+        <v>917</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-5.45</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -1165,16 +1167,16 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>22178275328</v>
+        <v>22104018944</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>30.580204</v>
+        <v>30.477816</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>14.154819</v>
+        <v>14.107426</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>2.8705988</v>
+        <v>2.8609877</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>13.2</v>
@@ -1229,7 +1231,7 @@
       <c r="X2" s="2" t="n"/>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T14:23:12+08:00</t>
+          <t>2026-09-10T14:25:37+08:00</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -1255,16 +1257,16 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>456598618112</v>
+        <v>438430302208</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>46.381737</v>
+        <v>44.66634</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>28.992168</v>
+        <v>27.838552</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>4.7206182</v>
+        <v>4.5327826</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>10.85</v>
@@ -1291,7 +1293,7 @@
         <v>159.5</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>20.59</v>
+        <v>20.53</v>
       </c>
       <c r="Q3" s="2" t="n">
         <v>32.93993</v>
@@ -1319,7 +1321,7 @@
       <c r="X3" s="2" t="n"/>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08T14:23:13+08:00</t>
+          <t>2026-09-10T14:25:38+08:00</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">

--- a/data/swing_user_watchlist_analysis.xlsx
+++ b/data/swing_user_watchlist_analysis.xlsx
@@ -613,17 +613,17 @@
         <v>90.3</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>89.3</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>-1.11</v>
+        <v>-4.65</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>T11-15中段</t>
+          <t>T16-20成熟</t>
         </is>
       </c>
       <c r="J2" s="2" t="n"/>
@@ -635,7 +635,7 @@
       <c r="P2" s="2" t="n"/>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10T14:25:37+08:00</t>
+          <t>2026-09-11T14:27:06+08:00</t>
         </is>
       </c>
     </row>
@@ -664,13 +664,13 @@
         <v>1010</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>917</v>
+        <v>902</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>-9.210000000000001</v>
+        <v>-10.69</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
       <c r="P3" s="2" t="n"/>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10T14:25:38+08:00</t>
+          <t>2026-09-11T14:27:07+08:00</t>
         </is>
       </c>
     </row>
@@ -862,17 +862,17 @@
         <v>90.3</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>89.3</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-1.11</v>
+        <v>-4.65</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>T11-15中段</t>
+          <t>T16-20成熟</t>
         </is>
       </c>
       <c r="H2" s="2" t="n">
@@ -882,7 +882,7 @@
         <v>-7.2</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-7.56</v>
+        <v>-10.87</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>5.43</v>
@@ -929,13 +929,13 @@
         <v>1010</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>917</v>
+        <v>902</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-9.210000000000001</v>
+        <v>-10.69</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         <v>-13.37</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>-9.699999999999999</v>
+        <v>-10.69</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>-9.699999999999999</v>
@@ -1167,16 +1167,16 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>22104018944</v>
+        <v>21311936512</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>30.477816</v>
+        <v>29.385664</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>14.107426</v>
+        <v>13.601895</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>2.8609877</v>
+        <v>2.758466</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>13.2</v>
@@ -1231,7 +1231,7 @@
       <c r="X2" s="2" t="n"/>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10T14:25:37+08:00</t>
+          <t>2026-09-11T14:27:06+08:00</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -1257,16 +1257,16 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>438430302208</v>
+        <v>431258566656</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>44.66634</v>
+        <v>43.91431</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>27.838552</v>
+        <v>27.383179</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>4.5327826</v>
+        <v>4.4586363</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>10.85</v>
@@ -1293,7 +1293,7 @@
         <v>159.5</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>20.53</v>
+        <v>20.54</v>
       </c>
       <c r="Q3" s="2" t="n">
         <v>32.93993</v>
@@ -1321,7 +1321,7 @@
       <c r="X3" s="2" t="n"/>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10T14:25:38+08:00</t>
+          <t>2026-09-11T14:27:07+08:00</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
